--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-geraeteprogrammierung.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-geraeteprogrammierung.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -1118,7 +1118,7 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-geraeteprogrammierung-mdc|2027.0.0-ballot.rc1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-kardio/ValueSet/mii-vs-kardio-geraeteprogrammierung-mdc|2027.0.0-ballot</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -2031,7 +2031,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="109.90234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="106.890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
